--- a/ig/DM-SEPTEMBRE-2026/CodeSystem-TRE-R248-ModeAcces.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/CodeSystem-TRE-R248-ModeAcces.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="65">
   <si>
     <t>Property</t>
   </si>
@@ -31,13 +31,13 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>OID:1.2.250.1.213.1.1.4.336</t>
+    <t>OID:1.2.250.1.213.1.1.4.248</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>20250131120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -116,6 +116,9 @@
   </si>
   <si>
     <t>Count</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>Code</t>
@@ -502,7 +505,9 @@
       <c r="A22" t="s" s="2">
         <v>33</v>
       </c>
-      <c r="B22" s="2"/>
+      <c r="B22" t="s" s="2">
+        <v>34</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -516,94 +521,94 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>21</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -618,51 +623,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D4" s="2"/>
     </row>
